--- a/forms/trg/Formulir_TRG_mnprg.xlsx
+++ b/forms/trg/Formulir_TRG_mnprg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B25)</f>
+        <f>COUNTA(Anggota!B5:B26)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F25)</f>
+        <f>COUNTA(Anggota!F5:F26)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,18 +913,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Rina Agustina</t>
+          <t>Prof. Dr. apt. Gemini Alam, M.Si</t>
         </is>
       </c>
       <c r="C5" s="12" t="n"/>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Metabolomics of Natural Products</t>
+          <t>Phytochemistry, Natural Product Chemistry, Metabolomics</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -933,7 +929,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>6507286881</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,10 +946,14 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Satria Astazaury Awal</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n"/>
+          <t>Rina Agustina</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Universitas Hasanuddin</t>
@@ -957,7 +961,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Natural Product Extraction and Identification</t>
+          <t>Metabolomics of Natural Products</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -979,10 +983,14 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>NURHASNI HASAN</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n"/>
+          <t>Satria Astazaury Awal</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Universitas Hasanuddin</t>
@@ -990,7 +998,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Drug Delivery Systems, Drug Formulation, Pharmaceutical Technology</t>
+          <t>Natural Product Extraction and Identification</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1012,10 +1020,14 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>ABDUL RAHIM</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n"/>
+          <t>NURHASNI HASAN</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Universitas Hasanuddin</t>
@@ -1023,7 +1035,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Phytochemistry, Pharmacognosy, Natural Product Isolation and Characterization</t>
+          <t>Drug Delivery Systems, Drug Formulation, Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1045,10 +1057,14 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Raihan</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n"/>
+          <t>ABDUL RAHIM</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Universitas Hasanuddin</t>
@@ -1056,7 +1072,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Phytochemistry, Analysis of Natural Products</t>
+          <t>Phytochemistry, Pharmacognosy, Natural Product Isolation and Characterization</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1078,22 +1094,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Alfi Khatib</t>
+          <t>Muhammad Raihan</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Internationa Islamic Universiti Malaysia</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Phytochemistry, Natural Product Chemistry, Metabolomics</t>
+          <t>Phytochemistry, Analysis of Natural Products</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1115,22 +1131,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Riki Andriawan</t>
+          <t>Alfi Khatib</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Internationa Islamic Universiti Malaysia</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Alkaloid Extraction</t>
+          <t>Phytochemistry, Natural Product Chemistry, Metabolomics</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1152,20 +1168,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Herwin</t>
+          <t>Riki Andriawan</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin, Universitas Muslim Indonesia</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n"/>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Alkaloid Extraction</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1185,17 +1205,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Moh. Whisnu Suryadhitama</t>
+          <t>Herwin</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Universitas Hasanuddin, Universitas Muslim Indonesia</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1216,10 +1236,26 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Moh. Whisnu Suryadhitama</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Nature has long been a treasure trove of bioactive compounds, offering solutions to some of humanity’s most pressing challenges in health, agriculture, and sustainability. At the Metabolomics and Natural Products Research Group, we harness the power of modern analytical science to explore this chemical diversity, decode its biological significance, and translate discoveries into real-world applications.</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1227,7 +1263,11 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1416,15 +1456,32 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_mnprg.xlsx
+++ b/forms/trg/Formulir_TRG_mnprg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. apt. Gemini Alam, M.Si</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
